--- a/InputData/elec/BPSpUGBCD/BAU Subsidy per Unit Grid Battery Capacity Deployed.xlsx
+++ b/InputData/elec/BPSpUGBCD/BAU Subsidy per Unit Grid Battery Capacity Deployed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/elec/BPSpUGBCD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\BPSpUGBCD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{4D1640CF-E3B7-443F-9523-22E8743CB9F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D5FB5CD-A50F-4A91-AB87-22AF1FE9269F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83145C88-A055-4C54-8A6E-232F6087B533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="960" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1710" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -444,24 +444,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -477,112 +477,115 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>0</v>
       </c>
       <c r="C2">
@@ -670,6 +673,9 @@
         <v>0</v>
       </c>
       <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
         <v>0</v>
       </c>
     </row>
@@ -823,6 +829,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -831,20 +843,37 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF93C7D9-506E-4DC5-802C-7B147B8B4C83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF93C7D9-506E-4DC5-802C-7B147B8B4C83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F57A316-8663-40A3-A070-BAAD7288E04B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C35D6C5-3E8F-4EA8-BB05-58D2B91BD254}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C35D6C5-3E8F-4EA8-BB05-58D2B91BD254}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F57A316-8663-40A3-A070-BAAD7288E04B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>